--- a/260907_RnD 자재창고 휴머노이드 잡할당 리스트_v0.1_검토요청.xlsx
+++ b/260907_RnD 자재창고 휴머노이드 잡할당 리스트_v0.1_검토요청.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0907" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1 (2)" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0910 재구성" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1 (2)" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0907'!$B$3:$H$172</definedName>
@@ -668,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K190"/>
+  <dimension ref="B1:K190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12.5" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
@@ -685,7 +686,8 @@
     <col width="11.08203125" bestFit="1" customWidth="1" style="24" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="1" s="24"/>
+    <row r="2" s="24">
       <c r="H2" s="19" t="inlineStr">
         <is>
           <t>LGES</t>
@@ -746,7 +748,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="24">
       <c r="B4" s="10" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -778,7 +780,7 @@
       <c r="J4" s="18" t="n"/>
       <c r="K4" s="3" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" s="24">
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -810,7 +812,7 @@
       <c r="J5" s="18" t="n"/>
       <c r="K5" s="3" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" s="24">
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -842,7 +844,7 @@
       <c r="J6" s="18" t="n"/>
       <c r="K6" s="3" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" s="24">
       <c r="B7" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -874,7 +876,7 @@
       <c r="J7" s="18" t="n"/>
       <c r="K7" s="3" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" s="24">
       <c r="B8" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -906,7 +908,7 @@
       <c r="J8" s="18" t="n"/>
       <c r="K8" s="3" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" s="24">
       <c r="B9" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -938,7 +940,7 @@
       <c r="J9" s="18" t="n"/>
       <c r="K9" s="3" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" s="24">
       <c r="B10" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -970,7 +972,7 @@
       <c r="J10" s="18" t="n"/>
       <c r="K10" s="3" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" s="24">
       <c r="B11" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1002,7 +1004,7 @@
       <c r="J11" s="18" t="n"/>
       <c r="K11" s="3" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" s="24">
       <c r="B12" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1099,7 +1101,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
@@ -1137,7 +1139,7 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
@@ -1175,7 +1177,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
@@ -1213,7 +1215,7 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
@@ -1289,7 +1291,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
@@ -1338,7 +1340,7 @@
       <c r="J20" s="18" t="n"/>
       <c r="K20" s="3" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" s="24">
       <c r="B21" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1370,7 +1372,7 @@
       <c r="J21" s="18" t="n"/>
       <c r="K21" s="3" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" s="24">
       <c r="B22" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1402,7 +1404,7 @@
       <c r="J22" s="18" t="n"/>
       <c r="K22" s="3" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" s="24">
       <c r="B23" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1434,7 +1436,7 @@
       <c r="J23" s="18" t="n"/>
       <c r="K23" s="3" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" s="24">
       <c r="B24" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1466,7 +1468,7 @@
       <c r="J24" s="18" t="n"/>
       <c r="K24" s="3" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" s="24">
       <c r="B25" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1498,7 +1500,7 @@
       <c r="J25" s="18" t="n"/>
       <c r="K25" s="3" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" s="24">
       <c r="B26" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1530,7 +1532,7 @@
       <c r="J26" s="18" t="n"/>
       <c r="K26" s="3" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" s="24">
       <c r="B27" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1562,7 +1564,7 @@
       <c r="J27" s="18" t="n"/>
       <c r="K27" s="3" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" s="24">
       <c r="B28" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1594,7 +1596,7 @@
       <c r="J28" s="18" t="n"/>
       <c r="K28" s="3" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" s="24">
       <c r="B29" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1626,7 +1628,7 @@
       <c r="J29" s="18" t="n"/>
       <c r="K29" s="3" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" s="24">
       <c r="B30" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1658,7 +1660,7 @@
       <c r="J30" s="18" t="n"/>
       <c r="K30" s="3" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" s="24">
       <c r="B31" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -1690,7 +1692,7 @@
       <c r="J31" s="18" t="n"/>
       <c r="K31" s="3" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" s="24">
       <c r="B32" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -3369,7 +3371,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Cell 흡착 + 바코드 스캔</t>
+          <t>Cell 흡착</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -3445,7 +3447,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>└ 바코드 스캔 (흡착 중 동시 수행 — 위 행에 합산)</t>
+          <t>Cell 바코드 스캔</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -3468,7 +3470,11 @@
       </c>
       <c r="I78" s="21" t="n"/>
       <c r="J78" s="18" t="n"/>
-      <c r="K78" s="3" t="n"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>흡착 중 동시 수행 — 시간은 바로 위 'Cell 흡착' 행(4s)에 합산</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="13" t="inlineStr">
@@ -4395,7 +4401,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Cell 흡착 + 바코드 스캔</t>
+          <t>Cell 흡착</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4471,7 +4477,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>└ 바코드 스캔 (흡착 중 동시 수행 — 위 행에 합산)</t>
+          <t>Cell 바코드 스캔</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4494,7 +4500,11 @@
       </c>
       <c r="I105" s="21" t="n"/>
       <c r="J105" s="18" t="n"/>
-      <c r="K105" s="3" t="n"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>흡착 중 동시 수행 — 시간은 바로 위 'Cell 흡착' 행(4s)에 합산</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="13" t="inlineStr">
@@ -5484,7 +5494,7 @@
       <c r="J131" s="18" t="n"/>
       <c r="K131" s="3" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" s="24">
       <c r="B132" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -5516,7 +5526,7 @@
       <c r="J132" s="18" t="n"/>
       <c r="K132" s="3" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" s="24">
       <c r="B133" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -5548,7 +5558,7 @@
       <c r="J133" s="18" t="n"/>
       <c r="K133" s="3" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" s="24">
       <c r="B134" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -5960,7 +5970,7 @@
       <c r="J144" s="18" t="n"/>
       <c r="K144" s="3" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" s="24">
       <c r="B145" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -5992,7 +6002,7 @@
       <c r="J145" s="18" t="n"/>
       <c r="K145" s="3" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" s="24">
       <c r="B146" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6024,7 +6034,7 @@
       <c r="J146" s="18" t="n"/>
       <c r="K146" s="3" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" s="24">
       <c r="B147" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6436,7 +6446,7 @@
       <c r="J157" s="18" t="n"/>
       <c r="K157" s="3" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" s="24">
       <c r="B158" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6468,7 +6478,7 @@
       <c r="J158" s="18" t="n"/>
       <c r="K158" s="3" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" s="24">
       <c r="B159" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6500,7 +6510,7 @@
       <c r="J159" s="18" t="n"/>
       <c r="K159" s="3" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" s="24">
       <c r="B160" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6532,7 +6542,7 @@
       <c r="J160" s="18" t="n"/>
       <c r="K160" s="3" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" s="24">
       <c r="B161" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6572,7 +6582,7 @@
       <c r="J161" s="18" t="n"/>
       <c r="K161" s="3" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" s="24">
       <c r="B162" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6612,7 +6622,7 @@
       <c r="J162" s="18" t="n"/>
       <c r="K162" s="3" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" s="24">
       <c r="B163" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6652,7 +6662,7 @@
       <c r="J163" s="18" t="n"/>
       <c r="K163" s="3" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" s="24">
       <c r="B164" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6692,7 +6702,7 @@
       <c r="J164" s="18" t="n"/>
       <c r="K164" s="3" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" s="24">
       <c r="B165" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6732,7 +6742,7 @@
       <c r="J165" s="18" t="n"/>
       <c r="K165" s="3" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" s="24">
       <c r="B166" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6772,7 +6782,7 @@
       <c r="J166" s="18" t="n"/>
       <c r="K166" s="3" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" s="24">
       <c r="B167" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6812,7 +6822,7 @@
       <c r="J167" s="18" t="n"/>
       <c r="K167" s="3" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" s="24">
       <c r="B168" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6852,7 +6862,7 @@
       <c r="J168" s="18" t="n"/>
       <c r="K168" s="3" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" s="24">
       <c r="B169" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6892,7 +6902,7 @@
       <c r="J169" s="18" t="n"/>
       <c r="K169" s="3" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" s="24">
       <c r="B170" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6932,7 +6942,7 @@
       <c r="J170" s="18" t="n"/>
       <c r="K170" s="3" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" s="24">
       <c r="B171" s="13" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -6972,7 +6982,7 @@
       <c r="J171" s="18" t="n"/>
       <c r="K171" s="3" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" s="24">
       <c r="B172" s="14" t="inlineStr">
         <is>
           <t>낱개 단위 출고</t>
@@ -7168,6 +7178,6471 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:K178"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.5" customWidth="1" style="24" min="2" max="2"/>
+    <col width="63.33203125" customWidth="1" style="24" min="3" max="3"/>
+    <col width="21.33203125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="9.9140625" customWidth="1" style="24" min="5" max="5"/>
+    <col width="26" customWidth="1" style="24" min="6" max="6"/>
+    <col width="16.5" customWidth="1" style="24" min="7" max="7"/>
+    <col width="15.9140625" customWidth="1" style="24" min="8" max="8"/>
+    <col width="2.75" customWidth="1" style="24" min="9" max="9"/>
+    <col width="15.83203125" customWidth="1" style="24" min="10" max="10"/>
+    <col width="40.58203125" customWidth="1" style="24" min="11" max="11"/>
+    <col width="12.9140625" customWidth="1" style="24" min="12" max="12"/>
+    <col width="11.08203125" customWidth="1" style="24" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="H2" s="19" t="inlineStr">
+        <is>
+          <t>LGES</t>
+        </is>
+      </c>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="inlineStr">
+        <is>
+          <t>LGCNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27.5" customHeight="1" s="24">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Lv1</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Lv2</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Lv3</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>수행</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>작업 구분</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>소요시간(sec, 사람)</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>자동화 요청(O/X)</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>자동화 검토(O/X)</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>사유(비고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Mini Kiva로 박스 테이핑 커팅기에 박스 공급</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>작업지시</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Mini Kiva로 박스 테이핑 커팅기에 박스 공급</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>이동(Box위치)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Mini Kiva로 박스 테이핑 커팅기에 박스 공급</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Mini Kiva로 박스 테이핑 커팅기에 박스 공급</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>이동(Box커팅기)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Mini Kiva로 박스 테이핑 커팅기에 박스 공급</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>박스 테이핑 커팅기로 테이핑 커팅</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Box 커팅</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Box 커팅기</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 테이프 커팅된 박스 소스 스테이션으로 이송</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 테이프 커팅된 박스 소스 스테이션으로 이송</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 테이프 커팅된 박스 소스 스테이션으로 이송</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>이미 소스 포지션에 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 인식 (BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box-lid 6회 (09/05~06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box-lid 6회 (09/05~06) 2.5~2.8s</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 흡착 (종이, 약한 힘)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box-lid 6회 (09/05~06) 전형 4.0s, 재시도 시 6~12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box-lid 6회 (09/05~06) 1.7s</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>뚜껑 핸드오프 (좌팔 컵 → 우팔 그리퍼)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box-lid 6회 (09/05~06) 최신 코드 4회 26.7~27.3s</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>이동(폐기 포지션)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 좌팔 home</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s(속도 0.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 드롭 (우팔 이동 + 그리퍼 개방)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>미실측 · 지정값 — 드롭까지 도달한 실행 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 우팔 home</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 소스 스테이션에 도착한 박스 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션 복귀)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>폐기 포지션 이동과 같은 경로 역방향 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / Tray 가 담긴 P-Box 공급</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>이동(Tray위치)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>이동(Tray 포지션)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>이동(공박스 위치)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>이동(Target 포지션)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>이동(공박스 위치)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>이동(잔량 포지션)</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Mini-Kiva로 잔량 / 타겟용 / 포장재 P-Box가 담긴 Tray 공급</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>이동(Target 포지션)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 인식 (BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 1.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 흡착</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 3.0s</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 1.3s</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 양팔 stow</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s(속도 0.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>이동(뚜껑 보관 위치)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>보관 위치 인식 + 섀시 정렬 (인식 3회, 미세이동 4회)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="n"/>
+      <c r="J43" s="18" t="n"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 8.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Arm 하강 · 릴리즈 · 상승</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I44" s="21" t="n"/>
+      <c r="J44" s="18" t="n"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 7.2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 양팔 home</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I45" s="21" t="n"/>
+      <c r="J45" s="18" t="n"/>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>이동(Tray 포지션)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I46" s="21" t="n"/>
+      <c r="J46" s="18" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 인식 (BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I47" s="21" t="n"/>
+      <c r="J47" s="18" t="n"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I48" s="21" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 1.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 흡착</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I49" s="21" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 3.0s</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I50" s="21" t="n"/>
+      <c r="J50" s="18" t="n"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 1.3s</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 양팔 stow</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I51" s="21" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s(속도 0.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>이동(뚜껑 보관 위치)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I52" s="21" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>보관 위치 인식 + 섀시 정렬 (인식 3회, 미세이동 4회)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I53" s="21" t="n"/>
+      <c r="J53" s="18" t="n"/>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 8.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Arm 하강 · 릴리즈 · 상승</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="n"/>
+      <c r="J54" s="18" t="n"/>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 7.2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 양팔 home</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="18" t="n"/>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>이동(잔량 포지션)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I56" s="21" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 인식 (BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I57" s="21" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I58" s="21" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 1.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 흡착</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 3.0s</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I60" s="21" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 1.3s</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 양팔 stow</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I61" s="21" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s(속도 0.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>이동(뚜껑 보관 위치)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I62" s="21" t="n"/>
+      <c r="J62" s="18" t="n"/>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>실측 09/09 `d` 대기 — 조이스틱 주행 미기록, 상한값</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>보관 위치 인식 + 섀시 정렬 (인식 3회, 미세이동 4회)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 8.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Arm 하강 · 릴리즈 · 상승</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I64" s="21" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>실측 --lid 1회 (09/09) 7.2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>휴머노이드로 P-Box 뚜껑 오픈 후 보관</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 양팔 home</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="18" t="n"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행 6.4s</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Tray 인식 (BEV)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I67" s="21" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Arm Tray 위로 접근</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Tray 흡착</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I69" s="21" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="18" t="n"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>이동(타겟 포지션, 0.5 m)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I71" s="21" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>타겟 인식 (주행 중 병행)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I72" s="21" t="n"/>
+      <c r="J72" s="18" t="n"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 주행 중 수행, 별도 시간 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Arm Tray 위로 접근</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I73" s="21" t="n"/>
+      <c r="J73" s="18" t="n"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Tray 내림 (코너 시트)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I74" s="21" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>타겟 P-Box에 Cell Tray / 포장재 이재</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I75" s="21" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box에서 Tray → Cell → Tray → Cell 순으로 해체하면서 Cell ID 판독</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션 복귀)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I76" s="21" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box에서 Tray → Cell → Tray → Cell 순으로 해체하면서 Cell ID 판독</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Cell 위치 산출 (Tray 인식 결과 기준, 필요 시 재인식)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I77" s="21" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 재인식 시 2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box에서 Tray → Cell → Tray → Cell 순으로 해체하면서 Cell ID 판독</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Arm Cell 위로 접근</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I78" s="21" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box에서 Tray → Cell → Tray → Cell 순으로 해체하면서 Cell ID 판독</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Cell 흡착 + 바코드 스캔 (동시)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I79" s="21" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 09/09 스캔 재시도 1회 13s</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box에서 Tray → Cell → Tray → Cell 순으로 해체하면서 Cell ID 판독</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I80" s="21" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box에서 Tray → Cell → Tray → Cell 순으로 해체하면서 Cell ID 판독</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Target 판정 (스캔 결과)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I81" s="21" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>즉시</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>출고 대상 Cell 타겟 P-Box로 이재</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>이동(타겟 P-Box, 0.55 m)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I82" s="21" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>출고 대상 Cell 타겟 P-Box로 이재</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>타겟 인식 (주행 중 병행)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I83" s="21" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 주행 중 수행, 별도 시간 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>출고 대상 Cell 타겟 P-Box로 이재</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Arm Cell 위로 접근</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I84" s="21" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>출고 대상 Cell 타겟 P-Box로 이재</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Cell 적재 (코너 시트)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I85" s="21" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>출고 대상 Cell 타겟 P-Box로 이재</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H86" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I86" s="21" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>출고 대상 Cell 타겟 P-Box로 이재</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션 복귀)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H87" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I87" s="21" t="n"/>
+      <c r="J87" s="18" t="n"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션 복귀)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I88" s="21" t="n"/>
+      <c r="J88" s="18" t="n"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Cell 위치 산출 (Tray 인식 결과 기준, 필요 시 재인식)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I89" s="21" t="n"/>
+      <c r="J89" s="18" t="n"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 재인식 시 2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Arm Cell 위로 접근</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I90" s="21" t="n"/>
+      <c r="J90" s="18" t="n"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Cell 흡착 + 바코드 스캔 (동시)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I91" s="21" t="n"/>
+      <c r="J91" s="18" t="n"/>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 09/09 스캔 재시도 1회 13s</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I92" s="21" t="n"/>
+      <c r="J92" s="18" t="n"/>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Target 판정 (스캔 결과)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I93" s="21" t="n"/>
+      <c r="J93" s="18" t="n"/>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>즉시</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>이동(잔량 P-Box, 0.5 m)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I94" s="21" t="n"/>
+      <c r="J94" s="18" t="n"/>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>타겟 인식 (주행 중 병행)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="n"/>
+      <c r="J95" s="18" t="n"/>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07) — 주행 중 수행, 별도 시간 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Arm Cell 위로 접근</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="n"/>
+      <c r="J96" s="18" t="n"/>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Cell 적재 (코너 시트)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H97" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I97" s="21" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I98" s="21" t="n"/>
+      <c r="J98" s="18" t="n"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>소스 Box 내 남은 포장재 및 Cell 전량을 잔량 P-Box로 이재(+Cell ID 스캔)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션 복귀)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I99" s="21" t="n"/>
+      <c r="J99" s="18" t="n"/>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>실측 run_item 65사이클 중앙값 (09/03~07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I100" s="21" t="n"/>
+      <c r="J100" s="18" t="n"/>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>이미 소스 포지션에 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>양팔 home + Box 인식 (BEV, 우팔)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="18" t="n"/>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box 1회 (09/09) 5.1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Arm Box 벽 위 hover 이동</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H102" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I102" s="21" t="n"/>
+      <c r="J102" s="18" t="n"/>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box 1회 (09/09) 8.6s (관절 이동 7.6s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>하강 + 그리퍼 파지</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I103" s="21" t="n"/>
+      <c r="J103" s="18" t="n"/>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box 1회 (09/09) 1.7s</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I104" s="21" t="n"/>
+      <c r="J104" s="18" t="n"/>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>실측 --box 1회 (09/09) 1.2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>이동(폐기 포지션)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H105" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="18" t="n"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>뚜껑 이동과 동일 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Box 드롭 (하강 + 그리퍼 개방)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I106" s="21" t="n"/>
+      <c r="J106" s="18" t="n"/>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>미실측 · 지정값 — `q`로 중단, 미실측</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션 복귀)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H107" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I107" s="21" t="n"/>
+      <c r="J107" s="18" t="n"/>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>뚜껑 이동과 동일 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>이동(뚜껑 보관 위치)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H108" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I108" s="21" t="n"/>
+      <c r="J108" s="18" t="n"/>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 양팔 stow</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I109" s="21" t="n"/>
+      <c r="J109" s="18" t="n"/>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 인식 (바닥, BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I110" s="21" t="n"/>
+      <c r="J110" s="18" t="n"/>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I111" s="21" t="n"/>
+      <c r="J111" s="18" t="n"/>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 흡착</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I112" s="21" t="n"/>
+      <c r="J112" s="18" t="n"/>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I113" s="21" t="n"/>
+      <c r="J113" s="18" t="n"/>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 양팔 home</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I114" s="21" t="n"/>
+      <c r="J114" s="18" t="n"/>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>이동(Target 포지션)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H115" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I115" s="21" t="n"/>
+      <c r="J115" s="18" t="n"/>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 인식 + 뚜껑 정렬</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H116" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I116" s="21" t="n"/>
+      <c r="J116" s="18" t="n"/>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순) — 테두리 정렬 로직 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Arm 하강 · 릴리즈 · 상승</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H117" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I117" s="21" t="n"/>
+      <c r="J117" s="18" t="n"/>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Kiva 호출</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I118" s="21" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="3" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I119" s="21" t="n"/>
+      <c r="J119" s="18" t="n"/>
+      <c r="K119" s="3" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C120" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>이동(하역위치)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="3" t="n"/>
+      <c r="H120" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I120" s="21" t="n"/>
+      <c r="J120" s="18" t="n"/>
+      <c r="K120" s="3" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="3" t="n"/>
+      <c r="H121" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I121" s="21" t="n"/>
+      <c r="J121" s="18" t="n"/>
+      <c r="K121" s="3" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>이동(뚜껑 보관 위치)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H122" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I122" s="21" t="n"/>
+      <c r="J122" s="18" t="n"/>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 양팔 stow</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I123" s="21" t="n"/>
+      <c r="J123" s="18" t="n"/>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 인식 (바닥, BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I124" s="21" t="n"/>
+      <c r="J124" s="18" t="n"/>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I125" s="21" t="n"/>
+      <c r="J125" s="18" t="n"/>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 흡착</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H126" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I126" s="21" t="n"/>
+      <c r="J126" s="18" t="n"/>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I127" s="21" t="n"/>
+      <c r="J127" s="18" t="n"/>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 양팔 home</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I128" s="21" t="n"/>
+      <c r="J128" s="18" t="n"/>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>이동(Tray 포지션)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I129" s="21" t="n"/>
+      <c r="J129" s="18" t="n"/>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 인식 + 뚜껑 정렬</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I130" s="21" t="n"/>
+      <c r="J130" s="18" t="n"/>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순) — 테두리 정렬 로직 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Arm 하강 · 릴리즈 · 상승</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I131" s="21" t="n"/>
+      <c r="J131" s="18" t="n"/>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I132" s="21" t="n"/>
+      <c r="J132" s="18" t="n"/>
+      <c r="K132" s="3" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C133" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>이동(Tray 위치)</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I133" s="21" t="n"/>
+      <c r="J133" s="18" t="n"/>
+      <c r="K133" s="3" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C134" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I134" s="21" t="n"/>
+      <c r="J134" s="18" t="n"/>
+      <c r="K134" s="3" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>이동(뚜껑 보관 위치)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I135" s="21" t="n"/>
+      <c r="J135" s="18" t="n"/>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>torso 기울임 + 양팔 stow</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I136" s="21" t="n"/>
+      <c r="J136" s="18" t="n"/>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 인식 (바닥, BEV + 깊이 보정)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I137" s="21" t="n"/>
+      <c r="J137" s="18" t="n"/>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Arm 뚜껑 위로 접근</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I138" s="21" t="n"/>
+      <c r="J138" s="18" t="n"/>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 흡착</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I139" s="21" t="n"/>
+      <c r="J139" s="18" t="n"/>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Arm 상승</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I140" s="21" t="n"/>
+      <c r="J140" s="18" t="n"/>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>torso 복귀 + 양팔 home</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I141" s="21" t="n"/>
+      <c r="J141" s="18" t="n"/>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>주행과 병행 전제 → 0. 현재 코드는 순차 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>이동(잔량 포지션)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H142" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I142" s="21" t="n"/>
+      <c r="J142" s="18" t="n"/>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 인식 + 뚜껑 정렬</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H143" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I143" s="21" t="n"/>
+      <c r="J143" s="18" t="n"/>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순) — 테두리 정렬 로직 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Arm 하강 · 릴리즈 · 상승</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H144" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I144" s="21" t="n"/>
+      <c r="J144" s="18" t="n"/>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>미구현 · 추정(--lid 역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C145" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>적재</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I145" s="21" t="n"/>
+      <c r="J145" s="18" t="n"/>
+      <c r="K145" s="3" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C146" s="13" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>이동(보관위치)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I146" s="21" t="n"/>
+      <c r="J146" s="18" t="n"/>
+      <c r="K146" s="3" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>낱개 피킹 완료된 박스는 폐기, P-Box는 뚜껑 결합 후 ACR 재적치</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>하역</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Kiva</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n"/>
+      <c r="G147" s="3" t="n"/>
+      <c r="H147" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I147" s="21" t="n"/>
+      <c r="J147" s="18" t="n"/>
+      <c r="K147" s="3" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션)</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I148" s="21" t="n"/>
+      <c r="J148" s="18" t="n"/>
+      <c r="K148" s="3" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C149" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Box 인식(Cell종류 인식)</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I149" s="21" t="n"/>
+      <c r="J149" s="18" t="n"/>
+      <c r="K149" s="3" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C150" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>착용 Tool 인식</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I150" s="21" t="n"/>
+      <c r="J150" s="18" t="n"/>
+      <c r="K150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>착용 Tool 적합성 판정(N)</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I151" s="21" t="n"/>
+      <c r="J151" s="18" t="n"/>
+      <c r="K151" s="3" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>이동(Tool 보관위치)</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I152" s="21" t="n"/>
+      <c r="J152" s="18" t="n"/>
+      <c r="K152" s="3" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C153" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Tool 인식</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I153" s="21" t="n"/>
+      <c r="J153" s="18" t="n"/>
+      <c r="K153" s="3" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>적합 Tool 확인</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H154" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I154" s="21" t="n"/>
+      <c r="J154" s="18" t="n"/>
+      <c r="K154" s="3" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C155" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>이동(착용 Tool 보관위치)</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I155" s="21" t="n"/>
+      <c r="J155" s="18" t="n"/>
+      <c r="K155" s="3" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C156" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>착용 Tool 제거</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I156" s="21" t="n"/>
+      <c r="J156" s="18" t="n"/>
+      <c r="K156" s="3" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>이동(적합 Tool 보관위치)</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H157" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I157" s="21" t="n"/>
+      <c r="J157" s="18" t="n"/>
+      <c r="K157" s="3" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="13" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>적합 Tool 착용</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H158" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I158" s="21" t="n"/>
+      <c r="J158" s="18" t="n"/>
+      <c r="K158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="14" t="inlineStr">
+        <is>
+          <t>낱개 단위 출고</t>
+        </is>
+      </c>
+      <c r="C159" s="14" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>이동(소스 포지션)</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>휴머노이드</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>산정중</t>
+        </is>
+      </c>
+      <c r="H159" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I159" s="21" t="n"/>
+      <c r="J159" s="18" t="n"/>
+      <c r="K159" s="3" t="n"/>
+    </row>
+    <row r="161">
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>Box 뚜껑 폐기</t>
+        </is>
+      </c>
+      <c r="G161" s="23">
+        <f>SUMIF($F$13:$F$159,F161,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>P-Box 뚜껑 보관</t>
+        </is>
+      </c>
+      <c r="G162" s="23">
+        <f>SUMIF($F$13:$F$159,F162,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>기본 포장 Tray(1EA) 이동</t>
+        </is>
+      </c>
+      <c r="G163" s="23">
+        <f>SUMIF($F$13:$F$159,F163,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Target Cell 판독</t>
+        </is>
+      </c>
+      <c r="G164" s="23">
+        <f>SUMIF($F$13:$F$159,F164,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>비 Target Cell 잔량 box 적재</t>
+        </is>
+      </c>
+      <c r="G165" s="23">
+        <f>SUMIF($F$13:$F$159,F165,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Box 폐기</t>
+        </is>
+      </c>
+      <c r="G166" s="23">
+        <f>SUMIF($F$13:$F$159,F166,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>P-Box 보관 뚜껑 재결합</t>
+        </is>
+      </c>
+      <c r="G167" s="23">
+        <f>SUMIF($F$13:$F$159,F167,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Tool 교체</t>
+        </is>
+      </c>
+      <c r="G168" s="23">
+        <f>SUMIF($F$13:$F$159,F168,$G$13:$G$159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>층 1개(Tray 1 + Cell 2) 소요 = Tray 이동 + Cell 2개 (Target/비Target 각 그룹 합계는 Cell 1개당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>[재구성 0910] 휴머노이드 행을 chassis_sequence.py 실제 흐름 순서로 다시 썼음. 원본 흐름은 '0907' 시트에 그대로 있음. 비고 열에 각 값의 근거를 표기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>[실측 근거] run_item 65사이클 중앙값(09/03~07) / --lid 1회, --box 1회(09/09) / --box-lid 픽·핸드오프 6회(09/05~06, 드롭은 0회). 초 단위 정수 반올림.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>[이동 값] 뚜껑·박스 태스크의 이동은 프롬프트~`d` 입력 사이 대기 시간(09/09 1회). 조이스틱 주행은 로그에 없어 상한값이며, 실제 거리가 나오면 늘어날 수 있음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>[병행 전제 0s] torso 기울임/복귀(각 6.4s, 속도 0.3)와 IK 모델 재빌드(각 5s)는 섀시 주행과 병행하는 것으로 보고 0. 현재 코드는 순차 실행이라 병행 구현 + 모델 캐시가 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>[타겟 인식 0s] Tray/Cell 적재 쪽 인식은 0.5 m 주행 중 수행되어 별도 시간이 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>[미실측] Box 뚜껑 드롭, Box 드롭(각 4s 지정값). Box 폐기의 이동은 뚜껑과 동일 가정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>[미구현] P-Box 보관 뚜껑 재결합: 코드 없음. --lid 역순으로 추정, 바닥 픽은 기울인 자세 필요·P-Box 테두리 정렬 로직 없음. Tool 교체: 산정중 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>[Box 폐기] --box 태스크(우팔 그리퍼로 박스 벽 파지 → 운반 → 드롭)를 새 그룹으로 추가. 원본에는 대응 그룹 없음.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
